--- a/tests/testdata/excel/フォルダ/ドット.付き.フォルダ/ドットフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/ドット.付き.フォルダ/ドットフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E9655B7-7035-462B-B493-FAD1FDAA0B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCFC9023-DB36-457D-AC35-BBE673D1DD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{B9ECF015-9E0B-408D-BA6F-65476C8664B3}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E45AECF9-6491-441D-9083-E740FC3D9764}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34633B4-B72E-4D55-93EF-5E656B177E11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BC0874-7032-4826-B66B-BE03FA85B180}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/ドット.付き.フォルダ/ドットフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/ドット.付き.フォルダ/ドットフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCFC9023-DB36-457D-AC35-BBE673D1DD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3C8DEAF-752A-44B0-A0CE-B7AA68770E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E45AECF9-6491-441D-9083-E740FC3D9764}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E52042D1-1A9A-4D0E-9866-D9EC659A2147}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BC0874-7032-4826-B66B-BE03FA85B180}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCBC4FC-FFE2-419E-AB4A-F0AF86BEC147}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
